--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -1,34 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kiele\PycharmProjects\Python-Selenium\PythonSeleniumProject1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gloria\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65E6AFAD-AF75-4C78-BD6B-A9CD38AF6CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3E55CD8-51F8-4441-B3E4-790493F86D3F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="6615"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -43,10 +32,10 @@
     <t>password</t>
   </si>
   <si>
+    <t>standard_user</t>
+  </si>
+  <si>
     <t>secret_sauce</t>
-  </si>
-  <si>
-    <t>standard_user</t>
   </si>
   <si>
     <t>problem_user</t>
@@ -58,7 +47,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -124,7 +113,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -136,7 +125,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -183,23 +172,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -235,23 +207,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -403,12 +358,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD66297-A564-45A9-A7F7-7A3F010C800C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -421,10 +376,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -432,7 +387,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -440,11 +395,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>